--- a/pyscripts/config.xlsx
+++ b/pyscripts/config.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10116"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\ShopifyAutoShirtPrinting\pyscripts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/claire/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC50411-76AA-4696-8322-2FD6EC30AC49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D6D0E1-0A4F-824A-91A3-ED039E86C0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="14020" activeTab="1" xr2:uid="{59B5C47C-A7C4-4284-8177-179D0BDAFBF5}"/>
+    <workbookView xWindow="9080" yWindow="900" windowWidth="24520" windowHeight="18400" activeTab="1" xr2:uid="{59B5C47C-A7C4-4284-8177-179D0BDAFBF5}"/>
   </bookViews>
   <sheets>
     <sheet name="PRODUCT TYPE" sheetId="1" r:id="rId1"/>
     <sheet name="Colors" sheetId="2" r:id="rId2"/>
     <sheet name="Fits" sheetId="3" r:id="rId3"/>
+    <sheet name="Styles" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="427">
   <si>
     <t>Tee</t>
   </si>
@@ -47,15 +48,9 @@
     <t>JPR</t>
   </si>
   <si>
-    <t>BLACK</t>
-  </si>
-  <si>
     <t>BLK</t>
   </si>
   <si>
-    <t>WHITE</t>
-  </si>
-  <si>
     <t>WHT</t>
   </si>
   <si>
@@ -68,19 +63,1252 @@
     <t>Long Sleeve</t>
   </si>
   <si>
-    <t>LS</t>
-  </si>
-  <si>
     <t>Regular</t>
   </si>
   <si>
     <t>REG</t>
   </si>
   <si>
-    <t>YELLOW</t>
-  </si>
-  <si>
     <t>YLW</t>
+  </si>
+  <si>
+    <t>Accessories</t>
+  </si>
+  <si>
+    <t>ACC</t>
+  </si>
+  <si>
+    <t>Hoodie</t>
+  </si>
+  <si>
+    <t>HOD</t>
+  </si>
+  <si>
+    <t>Pants</t>
+  </si>
+  <si>
+    <t>PNT</t>
+  </si>
+  <si>
+    <t>Tank</t>
+  </si>
+  <si>
+    <t>TNK</t>
+  </si>
+  <si>
+    <t>Dress</t>
+  </si>
+  <si>
+    <t>DRS</t>
+  </si>
+  <si>
+    <t>Shirt</t>
+  </si>
+  <si>
+    <t>SHI</t>
+  </si>
+  <si>
+    <t>Shorts</t>
+  </si>
+  <si>
+    <t>SHO</t>
+  </si>
+  <si>
+    <t>Skirt</t>
+  </si>
+  <si>
+    <t>SKT</t>
+  </si>
+  <si>
+    <t>Gift Cards</t>
+  </si>
+  <si>
+    <t>GFT</t>
+  </si>
+  <si>
+    <t>Jacket</t>
+  </si>
+  <si>
+    <t>JKT</t>
+  </si>
+  <si>
+    <t>Kids</t>
+  </si>
+  <si>
+    <t>KID</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>Acid Wash</t>
+  </si>
+  <si>
+    <t>ACD</t>
+  </si>
+  <si>
+    <t>Coal</t>
+  </si>
+  <si>
+    <t>COL</t>
+  </si>
+  <si>
+    <t>Charcoal</t>
+  </si>
+  <si>
+    <t>CHL</t>
+  </si>
+  <si>
+    <t>Faded Black</t>
+  </si>
+  <si>
+    <t>FBK</t>
+  </si>
+  <si>
+    <t>Graphite</t>
+  </si>
+  <si>
+    <t>GPT</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>BLU</t>
+  </si>
+  <si>
+    <t>Arctic Blue</t>
+  </si>
+  <si>
+    <t>ABL</t>
+  </si>
+  <si>
+    <t>Blue Jean</t>
+  </si>
+  <si>
+    <t>BLJ</t>
+  </si>
+  <si>
+    <t>Blue Spruce</t>
+  </si>
+  <si>
+    <t>BLS</t>
+  </si>
+  <si>
+    <t>Powder Blue</t>
+  </si>
+  <si>
+    <t>PWR</t>
+  </si>
+  <si>
+    <t>Carolina Blue</t>
+  </si>
+  <si>
+    <t>CBL</t>
+  </si>
+  <si>
+    <t>Chambray</t>
+  </si>
+  <si>
+    <t>CBY</t>
+  </si>
+  <si>
+    <t>Chestnut</t>
+  </si>
+  <si>
+    <t>CNT</t>
+  </si>
+  <si>
+    <t>Cobalt</t>
+  </si>
+  <si>
+    <t>CBT</t>
+  </si>
+  <si>
+    <t>Dark Denim</t>
+  </si>
+  <si>
+    <t>DDM</t>
+  </si>
+  <si>
+    <t>Denim</t>
+  </si>
+  <si>
+    <t>DNM</t>
+  </si>
+  <si>
+    <t>Faded Blue</t>
+  </si>
+  <si>
+    <t>FBL</t>
+  </si>
+  <si>
+    <t>Faded Slate</t>
+  </si>
+  <si>
+    <t>FSL</t>
+  </si>
+  <si>
+    <t>Indigo</t>
+  </si>
+  <si>
+    <t>IGO</t>
+  </si>
+  <si>
+    <t>Lagoon</t>
+  </si>
+  <si>
+    <t>LGN</t>
+  </si>
+  <si>
+    <t>Light Blue</t>
+  </si>
+  <si>
+    <t>LBL</t>
+  </si>
+  <si>
+    <t>Midnight</t>
+  </si>
+  <si>
+    <t>MDT</t>
+  </si>
+  <si>
+    <t>Navy</t>
+  </si>
+  <si>
+    <t>NVY</t>
+  </si>
+  <si>
+    <t>Navy Stone Wash</t>
+  </si>
+  <si>
+    <t>NSW</t>
+  </si>
+  <si>
+    <t>Ocean Ice Dye</t>
+  </si>
+  <si>
+    <t>OID</t>
+  </si>
+  <si>
+    <t>Pale Blue</t>
+  </si>
+  <si>
+    <t>PBL</t>
+  </si>
+  <si>
+    <t>Petrol Blue</t>
+  </si>
+  <si>
+    <t>PTL</t>
+  </si>
+  <si>
+    <t>Royal Blue</t>
+  </si>
+  <si>
+    <t>RYL</t>
+  </si>
+  <si>
+    <t>Seafoam</t>
+  </si>
+  <si>
+    <t>SFM</t>
+  </si>
+  <si>
+    <t>Slate</t>
+  </si>
+  <si>
+    <t>SLT</t>
+  </si>
+  <si>
+    <t>True Navy</t>
+  </si>
+  <si>
+    <t>TNY</t>
+  </si>
+  <si>
+    <t>Brown</t>
+  </si>
+  <si>
+    <t>BWN</t>
+  </si>
+  <si>
+    <t>Camel</t>
+  </si>
+  <si>
+    <t>CML</t>
+  </si>
+  <si>
+    <t>Clay</t>
+  </si>
+  <si>
+    <t>CLY</t>
+  </si>
+  <si>
+    <t>Walnut</t>
+  </si>
+  <si>
+    <t>WNT</t>
+  </si>
+  <si>
+    <t>Coffee</t>
+  </si>
+  <si>
+    <t>CFE</t>
+  </si>
+  <si>
+    <t>Copper</t>
+  </si>
+  <si>
+    <t>CPR</t>
+  </si>
+  <si>
+    <t>Dark Chocolate</t>
+  </si>
+  <si>
+    <t>DCH</t>
+  </si>
+  <si>
+    <t>Khaki</t>
+  </si>
+  <si>
+    <t>KKI</t>
+  </si>
+  <si>
+    <t>Musk</t>
+  </si>
+  <si>
+    <t>MSK</t>
+  </si>
+  <si>
+    <t>Tan</t>
+  </si>
+  <si>
+    <t>TAN</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>AMY</t>
+  </si>
+  <si>
+    <t>Avocado</t>
+  </si>
+  <si>
+    <t>AVO</t>
+  </si>
+  <si>
+    <t>Aqua</t>
+  </si>
+  <si>
+    <t>AQA</t>
+  </si>
+  <si>
+    <t>Bottle Green</t>
+  </si>
+  <si>
+    <t>BTL</t>
+  </si>
+  <si>
+    <t>Emerald</t>
+  </si>
+  <si>
+    <t>EMD</t>
+  </si>
+  <si>
+    <t>Faded Army</t>
+  </si>
+  <si>
+    <t>FAY</t>
+  </si>
+  <si>
+    <t>Faded Teal</t>
+  </si>
+  <si>
+    <t>FTL</t>
+  </si>
+  <si>
+    <t>Fern Ice Dye</t>
+  </si>
+  <si>
+    <t>FID</t>
+  </si>
+  <si>
+    <t>Forest Green</t>
+  </si>
+  <si>
+    <t>FST</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>GRN</t>
+  </si>
+  <si>
+    <t>Hemp</t>
+  </si>
+  <si>
+    <t>HMP</t>
+  </si>
+  <si>
+    <t>Jade</t>
+  </si>
+  <si>
+    <t>JDE</t>
+  </si>
+  <si>
+    <t>Lime</t>
+  </si>
+  <si>
+    <t>LME</t>
+  </si>
+  <si>
+    <t>Military Green</t>
+  </si>
+  <si>
+    <t>MGR</t>
+  </si>
+  <si>
+    <t>Moss Stone Wash</t>
+  </si>
+  <si>
+    <t>MSW</t>
+  </si>
+  <si>
+    <t>Pine Green</t>
+  </si>
+  <si>
+    <t>PNE</t>
+  </si>
+  <si>
+    <t>Pistachio</t>
+  </si>
+  <si>
+    <t>PTO</t>
+  </si>
+  <si>
+    <t>Sage</t>
+  </si>
+  <si>
+    <t>SGE</t>
+  </si>
+  <si>
+    <t>Sherbet</t>
+  </si>
+  <si>
+    <t>SBT</t>
+  </si>
+  <si>
+    <t>Teal</t>
+  </si>
+  <si>
+    <t>TEL</t>
+  </si>
+  <si>
+    <t>Grey</t>
+  </si>
+  <si>
+    <t>GRY</t>
+  </si>
+  <si>
+    <t>Grey Marle</t>
+  </si>
+  <si>
+    <t>Ash Stone Wash</t>
+  </si>
+  <si>
+    <t>ASW</t>
+  </si>
+  <si>
+    <t>Faded Dust</t>
+  </si>
+  <si>
+    <t>FDT</t>
+  </si>
+  <si>
+    <t>Light Grey</t>
+  </si>
+  <si>
+    <t>LGY</t>
+  </si>
+  <si>
+    <t>Marble Ice Dye</t>
+  </si>
+  <si>
+    <t>MID</t>
+  </si>
+  <si>
+    <t>Pepper</t>
+  </si>
+  <si>
+    <t>PPR</t>
+  </si>
+  <si>
+    <t>Storm</t>
+  </si>
+  <si>
+    <t>STM</t>
+  </si>
+  <si>
+    <t>Washed Grey</t>
+  </si>
+  <si>
+    <t>WGY</t>
+  </si>
+  <si>
+    <t>Multi</t>
+  </si>
+  <si>
+    <t>MTI</t>
+  </si>
+  <si>
+    <t>Camouflage</t>
+  </si>
+  <si>
+    <t>CMO</t>
+  </si>
+  <si>
+    <t>Autumn</t>
+  </si>
+  <si>
+    <t>ATM</t>
+  </si>
+  <si>
+    <t>Orange</t>
+  </si>
+  <si>
+    <t>ONG</t>
+  </si>
+  <si>
+    <t>Peach</t>
+  </si>
+  <si>
+    <t>PCH</t>
+  </si>
+  <si>
+    <t>Safety Orange</t>
+  </si>
+  <si>
+    <t>SON</t>
+  </si>
+  <si>
+    <t>Terracotta</t>
+  </si>
+  <si>
+    <t>TCA</t>
+  </si>
+  <si>
+    <t>Bubblegum</t>
+  </si>
+  <si>
+    <t>BBG</t>
+  </si>
+  <si>
+    <t>Faded Rose</t>
+  </si>
+  <si>
+    <t>FRS</t>
+  </si>
+  <si>
+    <t>Pale Pink</t>
+  </si>
+  <si>
+    <t>PPK</t>
+  </si>
+  <si>
+    <t>Pink</t>
+  </si>
+  <si>
+    <t>PNK</t>
+  </si>
+  <si>
+    <t>Rose</t>
+  </si>
+  <si>
+    <t>RSE</t>
+  </si>
+  <si>
+    <t>Salmon</t>
+  </si>
+  <si>
+    <t>SMN</t>
+  </si>
+  <si>
+    <t>Watermelon</t>
+  </si>
+  <si>
+    <t>WMN</t>
+  </si>
+  <si>
+    <t>Boysenberry</t>
+  </si>
+  <si>
+    <t>BSY</t>
+  </si>
+  <si>
+    <t>Faded Mauve</t>
+  </si>
+  <si>
+    <t>FMV</t>
+  </si>
+  <si>
+    <t>Fuchsia</t>
+  </si>
+  <si>
+    <t>FSA</t>
+  </si>
+  <si>
+    <t>Lavender</t>
+  </si>
+  <si>
+    <t>LVR</t>
+  </si>
+  <si>
+    <t>Mauve</t>
+  </si>
+  <si>
+    <t>MVE</t>
+  </si>
+  <si>
+    <t>Orchid</t>
+  </si>
+  <si>
+    <t>OCD</t>
+  </si>
+  <si>
+    <t>Orchid Stone Wash</t>
+  </si>
+  <si>
+    <t>OSW</t>
+  </si>
+  <si>
+    <t>Plum</t>
+  </si>
+  <si>
+    <t>PLM</t>
+  </si>
+  <si>
+    <t>Purple</t>
+  </si>
+  <si>
+    <t>PPL</t>
+  </si>
+  <si>
+    <t>Wine</t>
+  </si>
+  <si>
+    <t>WNE</t>
+  </si>
+  <si>
+    <t>Berry</t>
+  </si>
+  <si>
+    <t>BRY</t>
+  </si>
+  <si>
+    <t>Brick</t>
+  </si>
+  <si>
+    <t>BRK</t>
+  </si>
+  <si>
+    <t>Burgundy</t>
+  </si>
+  <si>
+    <t>BGY</t>
+  </si>
+  <si>
+    <t>Cardinal</t>
+  </si>
+  <si>
+    <t>CDL</t>
+  </si>
+  <si>
+    <t>Clay Ice Dye</t>
+  </si>
+  <si>
+    <t>CID</t>
+  </si>
+  <si>
+    <t>Coral</t>
+  </si>
+  <si>
+    <t>CRL</t>
+  </si>
+  <si>
+    <t>Crimson</t>
+  </si>
+  <si>
+    <t>CMN</t>
+  </si>
+  <si>
+    <t>Faded Wine</t>
+  </si>
+  <si>
+    <t>FWN</t>
+  </si>
+  <si>
+    <t>Paprika</t>
+  </si>
+  <si>
+    <t>PPA</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>RED</t>
+  </si>
+  <si>
+    <t>Stripe</t>
+  </si>
+  <si>
+    <t>STP</t>
+  </si>
+  <si>
+    <t>Black/White Stripe</t>
+  </si>
+  <si>
+    <t>BWS</t>
+  </si>
+  <si>
+    <t>Black/White Ringer</t>
+  </si>
+  <si>
+    <t>BWR</t>
+  </si>
+  <si>
+    <t>Blue/Black Stripe</t>
+  </si>
+  <si>
+    <t>BBS</t>
+  </si>
+  <si>
+    <t>Blue/White Stripe</t>
+  </si>
+  <si>
+    <t>Copper/Black Stripe</t>
+  </si>
+  <si>
+    <t>CBS</t>
+  </si>
+  <si>
+    <t>Green/Natural Stripe</t>
+  </si>
+  <si>
+    <t>GNS</t>
+  </si>
+  <si>
+    <t>Green/White Stripe</t>
+  </si>
+  <si>
+    <t>GWS</t>
+  </si>
+  <si>
+    <t>Navy/White Stripe</t>
+  </si>
+  <si>
+    <t>NWS</t>
+  </si>
+  <si>
+    <t>Red/Black Stripe</t>
+  </si>
+  <si>
+    <t>RBS</t>
+  </si>
+  <si>
+    <t>Red/Navy Stripe</t>
+  </si>
+  <si>
+    <t>RNS</t>
+  </si>
+  <si>
+    <t>Red/White Stripe</t>
+  </si>
+  <si>
+    <t>RWS</t>
+  </si>
+  <si>
+    <t>Red/White Ringer</t>
+  </si>
+  <si>
+    <t>RWR</t>
+  </si>
+  <si>
+    <t>White/Black Stripe</t>
+  </si>
+  <si>
+    <t>WBS</t>
+  </si>
+  <si>
+    <t>Yellow/Black Stripe</t>
+  </si>
+  <si>
+    <t>YBS</t>
+  </si>
+  <si>
+    <t>Yellow/White Stripe</t>
+  </si>
+  <si>
+    <t>YWS</t>
+  </si>
+  <si>
+    <t>Cream</t>
+  </si>
+  <si>
+    <t>CRM</t>
+  </si>
+  <si>
+    <t>Ecru</t>
+  </si>
+  <si>
+    <t>ECU</t>
+  </si>
+  <si>
+    <t>Natural</t>
+  </si>
+  <si>
+    <t>NTL</t>
+  </si>
+  <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>White Marle</t>
+  </si>
+  <si>
+    <t>WHM</t>
+  </si>
+  <si>
+    <t>Butter</t>
+  </si>
+  <si>
+    <t>BTR</t>
+  </si>
+  <si>
+    <t>Citrine Ice Dye</t>
+  </si>
+  <si>
+    <t>CLD</t>
+  </si>
+  <si>
+    <t>Faded Mustard</t>
+  </si>
+  <si>
+    <t>FMD</t>
+  </si>
+  <si>
+    <t>Safety Yellow</t>
+  </si>
+  <si>
+    <t>SYW</t>
+  </si>
+  <si>
+    <t>Yellow</t>
+  </si>
+  <si>
+    <t>Gold</t>
+  </si>
+  <si>
+    <t>GLD</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t>LMN</t>
+  </si>
+  <si>
+    <t>Mustard</t>
+  </si>
+  <si>
+    <t>MTD</t>
+  </si>
+  <si>
+    <t>Regular Tee</t>
+  </si>
+  <si>
+    <t>Vintage Fit</t>
+  </si>
+  <si>
+    <t>VTG</t>
+  </si>
+  <si>
+    <t>Vintage Tee</t>
+  </si>
+  <si>
+    <t>Oversized Tee</t>
+  </si>
+  <si>
+    <t>OSD</t>
+  </si>
+  <si>
+    <t>Maple</t>
+  </si>
+  <si>
+    <t>MPL</t>
+  </si>
+  <si>
+    <t>Maple Tee</t>
+  </si>
+  <si>
+    <t>Crop Tee</t>
+  </si>
+  <si>
+    <t>Long Sleeve Crop</t>
+  </si>
+  <si>
+    <t>LSC</t>
+  </si>
+  <si>
+    <t>Long Sleeve Crop Tee</t>
+  </si>
+  <si>
+    <t>LST</t>
+  </si>
+  <si>
+    <t>Long Sleeve Tee</t>
+  </si>
+  <si>
+    <t>Vintage Fit Long Sleeve</t>
+  </si>
+  <si>
+    <t>VLS</t>
+  </si>
+  <si>
+    <t>Vintage Long Sleeve Tee</t>
+  </si>
+  <si>
+    <t>Oversized Long Sleeve</t>
+  </si>
+  <si>
+    <t>OLS</t>
+  </si>
+  <si>
+    <t>Oversized Long Sleeve Tee</t>
+  </si>
+  <si>
+    <t>Raglan</t>
+  </si>
+  <si>
+    <t>RGN</t>
+  </si>
+  <si>
+    <t>Raglan Tee</t>
+  </si>
+  <si>
+    <t>Regular Jumper</t>
+  </si>
+  <si>
+    <t>Vintage Jumper</t>
+  </si>
+  <si>
+    <t>Oversized Jumper</t>
+  </si>
+  <si>
+    <t>Half  Zip Jumper</t>
+  </si>
+  <si>
+    <t>HZJ</t>
+  </si>
+  <si>
+    <t>Crop Jumper</t>
+  </si>
+  <si>
+    <t>Regular Hoodie</t>
+  </si>
+  <si>
+    <t>Crop Hoodie</t>
+  </si>
+  <si>
+    <t>Regular Track Pants</t>
+  </si>
+  <si>
+    <t>RTP</t>
+  </si>
+  <si>
+    <t>Maple Track Pants</t>
+  </si>
+  <si>
+    <t>MTP</t>
+  </si>
+  <si>
+    <t>Regular Chino Pants</t>
+  </si>
+  <si>
+    <t>CHO</t>
+  </si>
+  <si>
+    <t>Chino Pants</t>
+  </si>
+  <si>
+    <t>Madison Pants</t>
+  </si>
+  <si>
+    <t>MSN</t>
+  </si>
+  <si>
+    <t>Heavy Weight Shorts</t>
+  </si>
+  <si>
+    <t>HWS</t>
+  </si>
+  <si>
+    <t>Beach Shorts</t>
+  </si>
+  <si>
+    <t>BCH</t>
+  </si>
+  <si>
+    <t>Track Shorts</t>
+  </si>
+  <si>
+    <t>TRK</t>
+  </si>
+  <si>
+    <t>Walk Shorts</t>
+  </si>
+  <si>
+    <t>WLK</t>
+  </si>
+  <si>
+    <t>Chino Shorts</t>
+  </si>
+  <si>
+    <t>Linen Shorts</t>
+  </si>
+  <si>
+    <t>RLN</t>
+  </si>
+  <si>
+    <t>Regular Linen Shorts</t>
+  </si>
+  <si>
+    <t>Boardwalk Shorts</t>
+  </si>
+  <si>
+    <t>BWK</t>
+  </si>
+  <si>
+    <t>Maple Heavy Shorts</t>
+  </si>
+  <si>
+    <t>MHS</t>
+  </si>
+  <si>
+    <t>Perry Shorts</t>
+  </si>
+  <si>
+    <t>PRY</t>
+  </si>
+  <si>
+    <t>Jersey Shorts</t>
+  </si>
+  <si>
+    <t>JSY</t>
+  </si>
+  <si>
+    <t>Soft Shorts</t>
+  </si>
+  <si>
+    <t>SFT</t>
+  </si>
+  <si>
+    <t>Maple Linen Shorts</t>
+  </si>
+  <si>
+    <t>MLN</t>
+  </si>
+  <si>
+    <t>Madison Shorts</t>
+  </si>
+  <si>
+    <t>Denim Skirt</t>
+  </si>
+  <si>
+    <t>DSK</t>
+  </si>
+  <si>
+    <t>Sweat Skirt</t>
+  </si>
+  <si>
+    <t>SSK</t>
+  </si>
+  <si>
+    <t>Regular Polo</t>
+  </si>
+  <si>
+    <t>RPO</t>
+  </si>
+  <si>
+    <t>Maple Polo</t>
+  </si>
+  <si>
+    <t>MPO</t>
+  </si>
+  <si>
+    <t>Short Sleeve Shirt</t>
+  </si>
+  <si>
+    <t>SSS</t>
+  </si>
+  <si>
+    <t>Baseball Shirt</t>
+  </si>
+  <si>
+    <t>Work Jacket</t>
+  </si>
+  <si>
+    <t>WJT</t>
+  </si>
+  <si>
+    <t>Bomber Jacket</t>
+  </si>
+  <si>
+    <t>BJT</t>
+  </si>
+  <si>
+    <t>Short Sleeve Dress</t>
+  </si>
+  <si>
+    <t>SSD</t>
+  </si>
+  <si>
+    <t>Singlet Dress</t>
+  </si>
+  <si>
+    <t>STD</t>
+  </si>
+  <si>
+    <t>Long Sleeve Dress</t>
+  </si>
+  <si>
+    <t>LSD</t>
+  </si>
+  <si>
+    <t>Oversized Dress</t>
+  </si>
+  <si>
+    <t>Barnard</t>
+  </si>
+  <si>
+    <t>RTK</t>
+  </si>
+  <si>
+    <t>Regular Tank</t>
+  </si>
+  <si>
+    <t>Singlet</t>
+  </si>
+  <si>
+    <t>RST</t>
+  </si>
+  <si>
+    <t>Regular Singlet</t>
+  </si>
+  <si>
+    <t>Maple Tank</t>
+  </si>
+  <si>
+    <t>MTK</t>
+  </si>
+  <si>
+    <t>Crop Tank</t>
+  </si>
+  <si>
+    <t>CTK</t>
+  </si>
+  <si>
+    <t>Maple Singlet</t>
+  </si>
+  <si>
+    <t>MST</t>
+  </si>
+  <si>
+    <t>String Singlet</t>
+  </si>
+  <si>
+    <t>SST</t>
+  </si>
+  <si>
+    <t>Rugby Jersey</t>
+  </si>
+  <si>
+    <t>RGY</t>
+  </si>
+  <si>
+    <t>Leggings</t>
+  </si>
+  <si>
+    <t>LGG</t>
+  </si>
+  <si>
+    <t>Kids Tee</t>
+  </si>
+  <si>
+    <t>KTE</t>
+  </si>
+  <si>
+    <t>Kids Long Sleeve</t>
+  </si>
+  <si>
+    <t>KLS</t>
+  </si>
+  <si>
+    <t>Kids Long Sleeve Tee</t>
+  </si>
+  <si>
+    <t>Kids Jumper</t>
+  </si>
+  <si>
+    <t>KJR</t>
+  </si>
+  <si>
+    <t>Kids Hoodie</t>
+  </si>
+  <si>
+    <t>KHO</t>
+  </si>
+  <si>
+    <t>Kids Tank</t>
+  </si>
+  <si>
+    <t>KTK</t>
+  </si>
+  <si>
+    <t>Baby Tee</t>
+  </si>
+  <si>
+    <t>BTE</t>
+  </si>
+  <si>
+    <t>Baby Onesie</t>
+  </si>
+  <si>
+    <t>BOE</t>
+  </si>
+  <si>
+    <t>Parcel Tote</t>
+  </si>
+  <si>
+    <t>Carrie Tote</t>
+  </si>
+  <si>
+    <t>CTO</t>
+  </si>
+  <si>
+    <t>Shoulder Tote</t>
+  </si>
+  <si>
+    <t>STO</t>
+  </si>
+  <si>
+    <t>Army Green</t>
+  </si>
+  <si>
+    <t>Slate Blue</t>
   </si>
 </sst>
 </file>
@@ -432,10 +1660,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C776DDB2-1239-4EB3-8BB8-26BCEEBDCF01}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -443,7 +1671,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -451,12 +1679,100 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B13" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -466,10 +1782,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9972B5D-5D1B-43F4-B83E-8464E716D442}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B137"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -477,28 +1793,1092 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B6" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>49</v>
+      </c>
+      <c r="B9" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>51</v>
+      </c>
+      <c r="B10" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B16" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>67</v>
+      </c>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>69</v>
+      </c>
+      <c r="B19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+      <c r="B20" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>75</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>79</v>
+      </c>
+      <c r="B24" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>81</v>
+      </c>
+      <c r="B25" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>83</v>
+      </c>
+      <c r="B26" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>85</v>
+      </c>
+      <c r="B27" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>87</v>
+      </c>
+      <c r="B28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>91</v>
+      </c>
+      <c r="B30" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>93</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B32" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>99</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>101</v>
+      </c>
+      <c r="B35" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>103</v>
+      </c>
+      <c r="B36" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>107</v>
+      </c>
+      <c r="B38" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>109</v>
+      </c>
+      <c r="B39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>113</v>
+      </c>
+      <c r="B41" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>115</v>
+      </c>
+      <c r="B42" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>117</v>
+      </c>
+      <c r="B43" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>119</v>
+      </c>
+      <c r="B44" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>121</v>
+      </c>
+      <c r="B45" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>123</v>
+      </c>
+      <c r="B46" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>127</v>
+      </c>
+      <c r="B48" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>129</v>
+      </c>
+      <c r="B49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>131</v>
+      </c>
+      <c r="B50" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>133</v>
+      </c>
+      <c r="B51" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>135</v>
+      </c>
+      <c r="B52" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>137</v>
+      </c>
+      <c r="B53" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>139</v>
+      </c>
+      <c r="B54" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>143</v>
+      </c>
+      <c r="B56" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>145</v>
+      </c>
+      <c r="B57" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>149</v>
+      </c>
+      <c r="B59" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>151</v>
+      </c>
+      <c r="B60" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>153</v>
+      </c>
+      <c r="B61" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>155</v>
+      </c>
+      <c r="B62" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>157</v>
+      </c>
+      <c r="B63" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>159</v>
+      </c>
+      <c r="B64" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>161</v>
+      </c>
+      <c r="B65" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>166</v>
+      </c>
+      <c r="B68" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>168</v>
+      </c>
+      <c r="B69" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>172</v>
+      </c>
+      <c r="B71" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>176</v>
+      </c>
+      <c r="B73" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>178</v>
+      </c>
+      <c r="B74" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>180</v>
+      </c>
+      <c r="B75" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>182</v>
+      </c>
+      <c r="B76" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>184</v>
+      </c>
+      <c r="B77" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>186</v>
+      </c>
+      <c r="B78" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>188</v>
+      </c>
+      <c r="B79" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>190</v>
+      </c>
+      <c r="B80" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>192</v>
+      </c>
+      <c r="B81" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>194</v>
+      </c>
+      <c r="B82" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>196</v>
+      </c>
+      <c r="B83" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>198</v>
+      </c>
+      <c r="B84" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>200</v>
+      </c>
+      <c r="B85" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>202</v>
+      </c>
+      <c r="B86" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>204</v>
+      </c>
+      <c r="B87" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>206</v>
+      </c>
+      <c r="B88" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>208</v>
+      </c>
+      <c r="B89" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>210</v>
+      </c>
+      <c r="B90" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>212</v>
+      </c>
+      <c r="B91" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>214</v>
+      </c>
+      <c r="B92" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>216</v>
+      </c>
+      <c r="B93" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>218</v>
+      </c>
+      <c r="B94" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>220</v>
+      </c>
+      <c r="B95" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>222</v>
+      </c>
+      <c r="B96" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>224</v>
+      </c>
+      <c r="B97" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>226</v>
+      </c>
+      <c r="B98" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>228</v>
+      </c>
+      <c r="B99" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>230</v>
+      </c>
+      <c r="B100" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>232</v>
+      </c>
+      <c r="B101" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>234</v>
+      </c>
+      <c r="B102" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>236</v>
+      </c>
+      <c r="B103" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>238</v>
+      </c>
+      <c r="B104" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>240</v>
+      </c>
+      <c r="B105" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>242</v>
+      </c>
+      <c r="B106" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>244</v>
+      </c>
+      <c r="B107" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A108" t="s">
+        <v>246</v>
+      </c>
+      <c r="B108" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A109" t="s">
+        <v>248</v>
+      </c>
+      <c r="B109" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A110" t="s">
+        <v>250</v>
+      </c>
+      <c r="B110" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>252</v>
+      </c>
+      <c r="B111" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>253</v>
+      </c>
+      <c r="B112" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>255</v>
+      </c>
+      <c r="B113" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>257</v>
+      </c>
+      <c r="B114" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>259</v>
+      </c>
+      <c r="B115" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>261</v>
+      </c>
+      <c r="B116" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>263</v>
+      </c>
+      <c r="B117" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>265</v>
+      </c>
+      <c r="B118" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>267</v>
+      </c>
+      <c r="B119" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>269</v>
+      </c>
+      <c r="B120" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>271</v>
+      </c>
+      <c r="B121" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>273</v>
+      </c>
+      <c r="B122" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>275</v>
+      </c>
+      <c r="B123" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>277</v>
+      </c>
+      <c r="B124" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>279</v>
+      </c>
+      <c r="B125" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>281</v>
+      </c>
+      <c r="B126" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
-        <v>17</v>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>282</v>
+      </c>
+      <c r="B127" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>284</v>
+      </c>
+      <c r="B128" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>286</v>
+      </c>
+      <c r="B129" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>288</v>
+      </c>
+      <c r="B130" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>290</v>
+      </c>
+      <c r="B131" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>292</v>
+      </c>
+      <c r="B132" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>293</v>
+      </c>
+      <c r="B133" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>295</v>
+      </c>
+      <c r="B134" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A135" t="s">
+        <v>297</v>
+      </c>
+      <c r="B135" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>425</v>
+      </c>
+      <c r="B136" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>426</v>
+      </c>
+      <c r="B137" t="s">
+        <v>96</v>
       </c>
     </row>
   </sheetData>
@@ -508,14 +2888,14 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A948580C-FFA8-43C0-B012-282D53DB2C18}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B76"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -523,28 +2903,646 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>299</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>300</v>
+      </c>
+      <c r="B4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>303</v>
+      </c>
+      <c r="B6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>305</v>
+      </c>
+      <c r="B7" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>307</v>
+      </c>
+      <c r="B8" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>308</v>
+      </c>
+      <c r="B10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>309</v>
+      </c>
+      <c r="B11" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>311</v>
+      </c>
+      <c r="B12" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
         <v>10</v>
       </c>
+      <c r="B13" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>313</v>
+      </c>
+      <c r="B14" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>314</v>
+      </c>
+      <c r="B15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>319</v>
+      </c>
+      <c r="B18" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B19" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>322</v>
+      </c>
+      <c r="B20" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>324</v>
+      </c>
+      <c r="B22" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>325</v>
+      </c>
+      <c r="B23" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B25" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>329</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>330</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>331</v>
+      </c>
+      <c r="B28" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B29" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B30" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>337</v>
+      </c>
+      <c r="B31" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>338</v>
+      </c>
+      <c r="B32" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>340</v>
+      </c>
+      <c r="B33" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>342</v>
+      </c>
+      <c r="B34" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>344</v>
+      </c>
+      <c r="B35" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>346</v>
+      </c>
+      <c r="B36" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>348</v>
+      </c>
+      <c r="B37" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>349</v>
+      </c>
+      <c r="B38" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>351</v>
+      </c>
+      <c r="B39" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>352</v>
+      </c>
+      <c r="B40" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>354</v>
+      </c>
+      <c r="B41" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>356</v>
+      </c>
+      <c r="B42" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>358</v>
+      </c>
+      <c r="B43" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>360</v>
+      </c>
+      <c r="B44" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>362</v>
+      </c>
+      <c r="B45" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>364</v>
+      </c>
+      <c r="B46" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>365</v>
+      </c>
+      <c r="B47" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>367</v>
+      </c>
+      <c r="B48" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>369</v>
+      </c>
+      <c r="B49" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>371</v>
+      </c>
+      <c r="B50" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>373</v>
+      </c>
+      <c r="B51" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>375</v>
+      </c>
+      <c r="B52" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>376</v>
+      </c>
+      <c r="B53" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>378</v>
+      </c>
+      <c r="B54" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
+        <v>380</v>
+      </c>
+      <c r="B55" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>382</v>
+      </c>
+      <c r="B56" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>384</v>
+      </c>
+      <c r="B57" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>386</v>
+      </c>
+      <c r="B58" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>387</v>
+      </c>
+      <c r="B59" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>389</v>
+      </c>
+      <c r="B60" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>390</v>
+      </c>
+      <c r="B61" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>392</v>
+      </c>
+      <c r="B62" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>393</v>
+      </c>
+      <c r="B63" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>395</v>
+      </c>
+      <c r="B64" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>397</v>
+      </c>
+      <c r="B65" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>399</v>
+      </c>
+      <c r="B66" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>401</v>
+      </c>
+      <c r="B67" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>403</v>
+      </c>
+      <c r="B68" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>405</v>
+      </c>
+      <c r="B69" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>407</v>
+      </c>
+      <c r="B70" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>409</v>
+      </c>
+      <c r="B71" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>410</v>
+      </c>
+      <c r="B72" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>412</v>
+      </c>
+      <c r="B73" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>414</v>
+      </c>
+      <c r="B74" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>416</v>
+      </c>
+      <c r="B75" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>418</v>
+      </c>
+      <c r="B76" t="s">
+        <v>419</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13BC5A90-2265-C341-B996-ED2A9418E524}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>420</v>
+      </c>
       <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>421</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>14</v>
+        <v>423</v>
       </c>
       <c r="B4" t="s">
-        <v>15</v>
+        <v>424</v>
       </c>
     </row>
   </sheetData>
